--- a/SQL/ThinkSocial.xlsx
+++ b/SQL/ThinkSocial.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="30" windowWidth="20115" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="30" windowWidth="20115" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -422,7 +422,7 @@
         <v>8</v>
       </c>
       <c r="B1" t="str">
-        <f>"UNION ALL SELECT '"&amp;A1&amp;"','"&amp;A1&amp;".png', GETDATE(), GETDATE()"</f>
+        <f t="shared" ref="B1:B20" si="0">"UNION ALL SELECT '"&amp;A1&amp;"','"&amp;A1&amp;".png', GETDATE(), GETDATE()"</f>
         <v>UNION ALL SELECT 'Arsenal','Arsenal.png', GETDATE(), GETDATE()</v>
       </c>
       <c r="C1" t="str">
@@ -435,11 +435,11 @@
         <v>17</v>
       </c>
       <c r="B2" t="str">
-        <f>"UNION ALL SELECT '"&amp;A2&amp;"','"&amp;A2&amp;".png', GETDATE(), GETDATE()"</f>
+        <f t="shared" si="0"/>
         <v>UNION ALL SELECT 'Aston Villa','Aston Villa.png', GETDATE(), GETDATE()</v>
       </c>
       <c r="C2" t="str">
-        <f t="shared" ref="C2:C20" si="0">"UNION ALL SELECT '"&amp;A2&amp;"','Premier League'"</f>
+        <f t="shared" ref="C2:C20" si="1">"UNION ALL SELECT '"&amp;A2&amp;"','Premier League'"</f>
         <v>UNION ALL SELECT 'Aston Villa','Premier League'</v>
       </c>
     </row>
@@ -448,11 +448,11 @@
         <v>16</v>
       </c>
       <c r="B3" t="str">
-        <f>"UNION ALL SELECT '"&amp;A3&amp;"','"&amp;A3&amp;".png', GETDATE(), GETDATE()"</f>
+        <f t="shared" si="0"/>
         <v>UNION ALL SELECT 'Bournemouth','Bournemouth.png', GETDATE(), GETDATE()</v>
       </c>
       <c r="C3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>UNION ALL SELECT 'Bournemouth','Premier League'</v>
       </c>
     </row>
@@ -461,11 +461,11 @@
         <v>13</v>
       </c>
       <c r="B4" t="str">
-        <f>"UNION ALL SELECT '"&amp;A4&amp;"','"&amp;A4&amp;".png', GETDATE(), GETDATE()"</f>
+        <f t="shared" si="0"/>
         <v>UNION ALL SELECT 'Brighton','Brighton.png', GETDATE(), GETDATE()</v>
       </c>
       <c r="C4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>UNION ALL SELECT 'Brighton','Premier League'</v>
       </c>
     </row>
@@ -474,11 +474,11 @@
         <v>9</v>
       </c>
       <c r="B5" t="str">
-        <f>"UNION ALL SELECT '"&amp;A5&amp;"','"&amp;A5&amp;".png', GETDATE(), GETDATE()"</f>
+        <f t="shared" si="0"/>
         <v>UNION ALL SELECT 'Burnley','Burnley.png', GETDATE(), GETDATE()</v>
       </c>
       <c r="C5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>UNION ALL SELECT 'Burnley','Premier League'</v>
       </c>
     </row>
@@ -487,11 +487,11 @@
         <v>2</v>
       </c>
       <c r="B6" t="str">
-        <f>"UNION ALL SELECT '"&amp;A6&amp;"','"&amp;A6&amp;".png', GETDATE(), GETDATE()"</f>
+        <f t="shared" si="0"/>
         <v>UNION ALL SELECT 'Chelsea','Chelsea.png', GETDATE(), GETDATE()</v>
       </c>
       <c r="C6" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>UNION ALL SELECT 'Chelsea','Premier League'</v>
       </c>
     </row>
@@ -500,11 +500,11 @@
         <v>19</v>
       </c>
       <c r="B7" t="str">
-        <f>"UNION ALL SELECT '"&amp;A7&amp;"','"&amp;A7&amp;".png', GETDATE(), GETDATE()"</f>
+        <f t="shared" si="0"/>
         <v>UNION ALL SELECT 'Crystal Palace','Crystal Palace.png', GETDATE(), GETDATE()</v>
       </c>
       <c r="C7" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>UNION ALL SELECT 'Crystal Palace','Premier League'</v>
       </c>
     </row>
@@ -513,11 +513,11 @@
         <v>10</v>
       </c>
       <c r="B8" t="str">
-        <f>"UNION ALL SELECT '"&amp;A8&amp;"','"&amp;A8&amp;".png', GETDATE(), GETDATE()"</f>
+        <f t="shared" si="0"/>
         <v>UNION ALL SELECT 'Everton','Everton.png', GETDATE(), GETDATE()</v>
       </c>
       <c r="C8" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>UNION ALL SELECT 'Everton','Premier League'</v>
       </c>
     </row>
@@ -526,11 +526,11 @@
         <v>1</v>
       </c>
       <c r="B9" t="str">
-        <f>"UNION ALL SELECT '"&amp;A9&amp;"','"&amp;A9&amp;".png', GETDATE(), GETDATE()"</f>
+        <f t="shared" si="0"/>
         <v>UNION ALL SELECT 'Leicester City','Leicester City.png', GETDATE(), GETDATE()</v>
       </c>
       <c r="C9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>UNION ALL SELECT 'Leicester City','Premier League'</v>
       </c>
     </row>
@@ -539,11 +539,11 @@
         <v>0</v>
       </c>
       <c r="B10" t="str">
-        <f>"UNION ALL SELECT '"&amp;A10&amp;"','"&amp;A10&amp;".png', GETDATE(), GETDATE()"</f>
+        <f t="shared" si="0"/>
         <v>UNION ALL SELECT 'Liverpool','Liverpool.png', GETDATE(), GETDATE()</v>
       </c>
       <c r="C10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>UNION ALL SELECT 'Liverpool','Premier League'</v>
       </c>
     </row>
@@ -552,11 +552,11 @@
         <v>4</v>
       </c>
       <c r="B11" t="str">
-        <f>"UNION ALL SELECT '"&amp;A11&amp;"','"&amp;A11&amp;".png', GETDATE(), GETDATE()"</f>
+        <f t="shared" si="0"/>
         <v>UNION ALL SELECT 'Manchester City','Manchester City.png', GETDATE(), GETDATE()</v>
       </c>
       <c r="C11" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>UNION ALL SELECT 'Manchester City','Premier League'</v>
       </c>
     </row>
@@ -565,11 +565,11 @@
         <v>3</v>
       </c>
       <c r="B12" t="str">
-        <f>"UNION ALL SELECT '"&amp;A12&amp;"','"&amp;A12&amp;".png', GETDATE(), GETDATE()"</f>
+        <f t="shared" si="0"/>
         <v>UNION ALL SELECT 'Manchester United','Manchester United.png', GETDATE(), GETDATE()</v>
       </c>
       <c r="C12" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>UNION ALL SELECT 'Manchester United','Premier League'</v>
       </c>
     </row>
@@ -578,11 +578,11 @@
         <v>11</v>
       </c>
       <c r="B13" t="str">
-        <f>"UNION ALL SELECT '"&amp;A13&amp;"','"&amp;A13&amp;".png', GETDATE(), GETDATE()"</f>
+        <f t="shared" si="0"/>
         <v>UNION ALL SELECT 'Newcastle United','Newcastle United.png', GETDATE(), GETDATE()</v>
       </c>
       <c r="C13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>UNION ALL SELECT 'Newcastle United','Premier League'</v>
       </c>
     </row>
@@ -591,11 +591,11 @@
         <v>18</v>
       </c>
       <c r="B14" t="str">
-        <f>"UNION ALL SELECT '"&amp;A14&amp;"','"&amp;A14&amp;".png', GETDATE(), GETDATE()"</f>
+        <f t="shared" si="0"/>
         <v>UNION ALL SELECT 'Norwich City','Norwich City.png', GETDATE(), GETDATE()</v>
       </c>
       <c r="C14" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>UNION ALL SELECT 'Norwich City','Premier League'</v>
       </c>
     </row>
@@ -604,11 +604,11 @@
         <v>5</v>
       </c>
       <c r="B15" t="str">
-        <f>"UNION ALL SELECT '"&amp;A15&amp;"','"&amp;A15&amp;".png', GETDATE(), GETDATE()"</f>
+        <f t="shared" si="0"/>
         <v>UNION ALL SELECT 'Sheffield United','Sheffield United.png', GETDATE(), GETDATE()</v>
       </c>
       <c r="C15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>UNION ALL SELECT 'Sheffield United','Premier League'</v>
       </c>
     </row>
@@ -617,11 +617,11 @@
         <v>12</v>
       </c>
       <c r="B16" t="str">
-        <f>"UNION ALL SELECT '"&amp;A16&amp;"','"&amp;A16&amp;".png', GETDATE(), GETDATE()"</f>
+        <f t="shared" si="0"/>
         <v>UNION ALL SELECT 'Southampton','Southampton.png', GETDATE(), GETDATE()</v>
       </c>
       <c r="C16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>UNION ALL SELECT 'Southampton','Premier League'</v>
       </c>
     </row>
@@ -630,11 +630,11 @@
         <v>7</v>
       </c>
       <c r="B17" t="str">
-        <f>"UNION ALL SELECT '"&amp;A17&amp;"','"&amp;A17&amp;".png', GETDATE(), GETDATE()"</f>
+        <f t="shared" si="0"/>
         <v>UNION ALL SELECT 'Tottenham Hotspur','Tottenham Hotspur.png', GETDATE(), GETDATE()</v>
       </c>
       <c r="C17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>UNION ALL SELECT 'Tottenham Hotspur','Premier League'</v>
       </c>
     </row>
@@ -643,11 +643,11 @@
         <v>15</v>
       </c>
       <c r="B18" t="str">
-        <f>"UNION ALL SELECT '"&amp;A18&amp;"','"&amp;A18&amp;".png', GETDATE(), GETDATE()"</f>
+        <f t="shared" si="0"/>
         <v>UNION ALL SELECT 'Watford','Watford.png', GETDATE(), GETDATE()</v>
       </c>
       <c r="C18" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>UNION ALL SELECT 'Watford','Premier League'</v>
       </c>
     </row>
@@ -656,11 +656,11 @@
         <v>14</v>
       </c>
       <c r="B19" t="str">
-        <f>"UNION ALL SELECT '"&amp;A19&amp;"','"&amp;A19&amp;".png', GETDATE(), GETDATE()"</f>
+        <f t="shared" si="0"/>
         <v>UNION ALL SELECT 'West Ham','West Ham.png', GETDATE(), GETDATE()</v>
       </c>
       <c r="C19" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>UNION ALL SELECT 'West Ham','Premier League'</v>
       </c>
     </row>
@@ -669,11 +669,11 @@
         <v>6</v>
       </c>
       <c r="B20" t="str">
-        <f>"UNION ALL SELECT '"&amp;A20&amp;"','"&amp;A20&amp;".png', GETDATE(), GETDATE()"</f>
+        <f t="shared" si="0"/>
         <v>UNION ALL SELECT 'Wolves','Wolves.png', GETDATE(), GETDATE()</v>
       </c>
       <c r="C20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>UNION ALL SELECT 'Wolves','Premier League'</v>
       </c>
     </row>
@@ -687,7 +687,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
@@ -735,7 +735,7 @@
         <v>0.6875</v>
       </c>
       <c r="H2" t="str">
-        <f t="shared" ref="H2:H30" si="0">"UNION ALL SELECT '"&amp;C2&amp;"','"&amp;D2&amp;"','"&amp;TEXT(E2,"DD MMM YY")&amp;" "&amp;TEXT(F2,"HH:MM:SS")&amp;"'"</f>
+        <f t="shared" ref="H2:H39" si="0">"UNION ALL SELECT '"&amp;C2&amp;"','"&amp;D2&amp;"','"&amp;TEXT(E2,"DD MMM YY")&amp;" "&amp;TEXT(F2,"HH:MM:SS")&amp;"'"</f>
         <v>UNION ALL SELECT 'Watford','Southampton','28 Jun 20 16:30:00'</v>
       </c>
     </row>
@@ -870,7 +870,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D9" t="s">
         <v>7</v>
@@ -883,7 +883,7 @@
       </c>
       <c r="H9" t="str">
         <f t="shared" si="0"/>
-        <v>UNION ALL SELECT 'Southampton','Tottenham Hotspur','02 Jul 20 18:00:00'</v>
+        <v>UNION ALL SELECT 'Sheffield United','Tottenham Hotspur','02 Jul 20 18:00:00'</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -912,20 +912,20 @@
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E11" s="2">
         <v>44016</v>
       </c>
       <c r="F11" s="1">
-        <v>0.625</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="H11" t="str">
-        <f t="shared" si="0"/>
-        <v>UNION ALL SELECT 'Burnley','Sheffield United','04 Jul 20 15:00:00'</v>
+        <f>"UNION ALL SELECT '"&amp;C11&amp;"','"&amp;D11&amp;"','"&amp;TEXT(E11,"DD MMM YY")&amp;" "&amp;TEXT(F11,"HH:MM:SS")&amp;"'"</f>
+        <v>UNION ALL SELECT 'Norwich City','Brighton','04 Jul 20 12:30:00'</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -933,10 +933,10 @@
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E12" s="2">
         <v>44016</v>
@@ -945,8 +945,8 @@
         <v>0.625</v>
       </c>
       <c r="H12" t="str">
-        <f t="shared" si="0"/>
-        <v>UNION ALL SELECT 'Chelsea','Watford','04 Jul 20 15:00:00'</v>
+        <f>"UNION ALL SELECT '"&amp;C12&amp;"','"&amp;D12&amp;"','"&amp;TEXT(E12,"DD MMM YY")&amp;" "&amp;TEXT(F12,"HH:MM:SS")&amp;"'"</f>
+        <v>UNION ALL SELECT 'Leicester City','Crystal Palace','04 Jul 20 15:00:00'</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -954,10 +954,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E13" s="2">
         <v>44016</v>
@@ -966,8 +966,8 @@
         <v>0.625</v>
       </c>
       <c r="H13" t="str">
-        <f t="shared" si="0"/>
-        <v>UNION ALL SELECT 'Leicester City','Crystal Palace','04 Jul 20 15:00:00'</v>
+        <f>"UNION ALL SELECT '"&amp;C13&amp;"','"&amp;D13&amp;"','"&amp;TEXT(E13,"DD MMM YY")&amp;" "&amp;TEXT(F13,"HH:MM:SS")&amp;"'"</f>
+        <v>UNION ALL SELECT 'Manchester United','Bournemouth','04 Jul 20 15:00:00'</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -975,20 +975,20 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D14" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2">
         <v>44016</v>
       </c>
       <c r="F14" s="1">
-        <v>0.625</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="H14" t="str">
-        <f t="shared" si="0"/>
-        <v>UNION ALL SELECT 'Liverpool','Aston Villa','04 Jul 20 15:00:00'</v>
+        <f>"UNION ALL SELECT '"&amp;C14&amp;"','"&amp;D14&amp;"','"&amp;TEXT(E14,"DD MMM YY")&amp;" "&amp;TEXT(F14,"HH:MM:SS")&amp;"'"</f>
+        <v>UNION ALL SELECT 'Wolves','Arsenal','04 Jul 20 17:30:00'</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -996,20 +996,20 @@
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E15" s="2">
         <v>44016</v>
       </c>
       <c r="F15" s="1">
-        <v>0.625</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="H15" t="str">
-        <f t="shared" si="0"/>
-        <v>UNION ALL SELECT 'Manchester United','Bournemouth','04 Jul 20 15:00:00'</v>
+        <f>"UNION ALL SELECT '"&amp;C15&amp;"','"&amp;D15&amp;"','"&amp;TEXT(E15,"DD MMM YY")&amp;" "&amp;TEXT(F15,"HH:MM:SS")&amp;"'"</f>
+        <v>UNION ALL SELECT 'Chelsea','Watford','04 Jul 20 20:00:00'</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1017,20 +1017,20 @@
         <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D16" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E16" s="2">
-        <v>44016</v>
+        <v>44017</v>
       </c>
       <c r="F16" s="1">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="H16" t="str">
-        <f t="shared" si="0"/>
-        <v>UNION ALL SELECT 'Newcastle United','West Ham','04 Jul 20 15:00:00'</v>
+        <f>"UNION ALL SELECT '"&amp;C16&amp;"','"&amp;D16&amp;"','"&amp;TEXT(E16,"DD MMM YY")&amp;" "&amp;TEXT(F16,"HH:MM:SS")&amp;"'"</f>
+        <v>UNION ALL SELECT 'Burnley','Sheffield United','05 Jul 20 12:00:00'</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1038,20 +1038,20 @@
         <v>7</v>
       </c>
       <c r="C17" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E17" s="2">
-        <v>44016</v>
+        <v>44017</v>
       </c>
       <c r="F17" s="1">
-        <v>0.625</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="H17" t="str">
-        <f t="shared" si="0"/>
-        <v>UNION ALL SELECT 'Norwich City','Brighton','04 Jul 20 15:00:00'</v>
+        <f>"UNION ALL SELECT '"&amp;C17&amp;"','"&amp;D17&amp;"','"&amp;TEXT(E17,"DD MMM YY")&amp;" "&amp;TEXT(F17,"HH:MM:SS")&amp;"'"</f>
+        <v>UNION ALL SELECT 'Newcastle United','West Ham','05 Jul 20 14:00:00'</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1059,20 +1059,20 @@
         <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D18" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="E18" s="2">
-        <v>44016</v>
+        <v>44017</v>
       </c>
       <c r="F18" s="1">
-        <v>0.625</v>
+        <v>0.6875</v>
       </c>
       <c r="H18" t="str">
-        <f t="shared" si="0"/>
-        <v>UNION ALL SELECT 'Southampton','Manchester City','04 Jul 20 15:00:00'</v>
+        <f>"UNION ALL SELECT '"&amp;C18&amp;"','"&amp;D18&amp;"','"&amp;TEXT(E18,"DD MMM YY")&amp;" "&amp;TEXT(F18,"HH:MM:SS")&amp;"'"</f>
+        <v>UNION ALL SELECT 'Liverpool','Aston Villa','05 Jul 20 16:30:00'</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1080,20 +1080,20 @@
         <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D19" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E19" s="2">
-        <v>44016</v>
+        <v>44017</v>
       </c>
       <c r="F19" s="1">
-        <v>0.625</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="H19" t="str">
-        <f t="shared" si="0"/>
-        <v>UNION ALL SELECT 'Tottenham Hotspur','Everton','04 Jul 20 15:00:00'</v>
+        <f>"UNION ALL SELECT '"&amp;C19&amp;"','"&amp;D19&amp;"','"&amp;TEXT(E19,"DD MMM YY")&amp;" "&amp;TEXT(F19,"HH:MM:SS")&amp;"'"</f>
+        <v>UNION ALL SELECT 'Southampton','Manchester City','05 Jul 20 19:00:00'</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1101,201 +1101,205 @@
         <v>6</v>
       </c>
       <c r="C20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D20" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E20" s="2">
-        <v>44016</v>
+        <v>44018</v>
       </c>
       <c r="F20" s="1">
-        <v>0.625</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="H20" t="str">
-        <f t="shared" si="0"/>
-        <v>UNION ALL SELECT 'Wolves','Arsenal','04 Jul 20 15:00:00'</v>
+        <f>"UNION ALL SELECT '"&amp;C20&amp;"','"&amp;D20&amp;"','"&amp;TEXT(E20,"DD MMM YY")&amp;" "&amp;TEXT(F20,"HH:MM:SS")&amp;"'"</f>
+        <v>UNION ALL SELECT 'Tottenham Hotspur','Everton','06 Jul 20 20:00:00'</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="C21" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D21" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E21" s="2">
-        <v>44020</v>
+        <v>44019</v>
       </c>
       <c r="F21" s="1">
-        <v>0.83333333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="H21" t="str">
-        <f t="shared" si="0"/>
-        <v>UNION ALL SELECT 'Bournemouth','Tottenham Hotspur','08 Jul 20 20:00:00'</v>
+        <f>"UNION ALL SELECT '"&amp;C21&amp;"','"&amp;D21&amp;"','"&amp;TEXT(E21,"DD MMM YY")&amp;" "&amp;TEXT(F21,"HH:MM:SS")&amp;"'"</f>
+        <v>UNION ALL SELECT 'Crystal Palace','Chelsea','07 Jul 20 18:00:00'</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="C22" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D22" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E22" s="2">
-        <v>44020</v>
+        <v>44019</v>
       </c>
       <c r="F22" s="1">
-        <v>0.83333333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="H22" t="str">
-        <f t="shared" si="0"/>
-        <v>UNION ALL SELECT 'Arsenal','Leicester City','08 Jul 20 20:00:00'</v>
+        <f>"UNION ALL SELECT '"&amp;C22&amp;"','"&amp;D22&amp;"','"&amp;TEXT(E22,"DD MMM YY")&amp;" "&amp;TEXT(F22,"HH:MM:SS")&amp;"'"</f>
+        <v>UNION ALL SELECT 'Watford','Norwich City','07 Jul 20 18:00:00'</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="C23" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D23" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23" s="2">
-        <v>44020</v>
+        <v>44019</v>
       </c>
       <c r="F23" s="1">
-        <v>0.83333333333333337</v>
+        <v>0.84375</v>
       </c>
       <c r="H23" t="str">
-        <f t="shared" si="0"/>
-        <v>UNION ALL SELECT 'Aston Villa','Manchester United','08 Jul 20 20:00:00'</v>
+        <f>"UNION ALL SELECT '"&amp;C23&amp;"','"&amp;D23&amp;"','"&amp;TEXT(E23,"DD MMM YY")&amp;" "&amp;TEXT(F23,"HH:MM:SS")&amp;"'"</f>
+        <v>UNION ALL SELECT 'Arsenal','Leicester City','07 Jul 20 20:15:00'</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="C24" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D24" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E24" s="2">
         <v>44020</v>
       </c>
       <c r="F24" s="1">
-        <v>0.83333333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="H24" t="str">
-        <f t="shared" si="0"/>
-        <v>UNION ALL SELECT 'Brighton','Liverpool','08 Jul 20 20:00:00'</v>
+        <f>"UNION ALL SELECT '"&amp;C24&amp;"','"&amp;D24&amp;"','"&amp;TEXT(E24,"DD MMM YY")&amp;" "&amp;TEXT(F24,"HH:MM:SS")&amp;"'"</f>
+        <v>UNION ALL SELECT 'Manchester City','Newcastle United','08 Jul 20 18:00:00'</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="C25" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E25" s="2">
         <v>44020</v>
       </c>
       <c r="F25" s="1">
-        <v>0.83333333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="H25" t="str">
-        <f t="shared" si="0"/>
-        <v>UNION ALL SELECT 'Crystal Palace','Chelsea','08 Jul 20 20:00:00'</v>
+        <f>"UNION ALL SELECT '"&amp;C25&amp;"','"&amp;D25&amp;"','"&amp;TEXT(E25,"DD MMM YY")&amp;" "&amp;TEXT(F25,"HH:MM:SS")&amp;"'"</f>
+        <v>UNION ALL SELECT 'Sheffield United','Wolves','08 Jul 20 18:00:00'</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="C26" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D26" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E26" s="2">
         <v>44020</v>
       </c>
       <c r="F26" s="1">
-        <v>0.83333333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="H26" t="str">
-        <f t="shared" si="0"/>
-        <v>UNION ALL SELECT 'Everton','Southampton','08 Jul 20 20:00:00'</v>
+        <f>"UNION ALL SELECT '"&amp;C26&amp;"','"&amp;D26&amp;"','"&amp;TEXT(E26,"DD MMM YY")&amp;" "&amp;TEXT(F26,"HH:MM:SS")&amp;"'"</f>
+        <v>UNION ALL SELECT 'West Ham','Burnley','08 Jul 20 18:00:00'</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="C27" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E27" s="2">
         <v>44020</v>
       </c>
       <c r="F27" s="1">
-        <v>0.83333333333333337</v>
+        <v>0.84375</v>
       </c>
       <c r="H27" t="str">
-        <f t="shared" si="0"/>
-        <v>UNION ALL SELECT 'Manchester City','Newcastle United','08 Jul 20 20:00:00'</v>
+        <f>"UNION ALL SELECT '"&amp;C27&amp;"','"&amp;D27&amp;"','"&amp;TEXT(E27,"DD MMM YY")&amp;" "&amp;TEXT(F27,"HH:MM:SS")&amp;"'"</f>
+        <v>UNION ALL SELECT 'Brighton','Liverpool','08 Jul 20 20:15:00'</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="C28" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D28" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E28" s="2">
-        <v>44020</v>
+        <v>44021</v>
       </c>
       <c r="F28" s="1">
-        <v>0.83333333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="H28" t="str">
-        <f t="shared" si="0"/>
-        <v>UNION ALL SELECT 'Sheffield United','Wolves','08 Jul 20 20:00:00'</v>
+        <f>"UNION ALL SELECT '"&amp;C28&amp;"','"&amp;D28&amp;"','"&amp;TEXT(E28,"DD MMM YY")&amp;" "&amp;TEXT(F28,"HH:MM:SS")&amp;"'"</f>
+        <v>UNION ALL SELECT 'Bournemouth','Tottenham Hotspur','09 Jul 20 18:00:00'</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="C29" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D29" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E29" s="2">
-        <v>44020</v>
+        <v>44021</v>
       </c>
       <c r="F29" s="1">
-        <v>0.83333333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="H29" t="str">
-        <f t="shared" si="0"/>
-        <v>UNION ALL SELECT 'Watford','Norwich City','08 Jul 20 20:00:00'</v>
+        <f>"UNION ALL SELECT '"&amp;C29&amp;"','"&amp;D29&amp;"','"&amp;TEXT(E29,"DD MMM YY")&amp;" "&amp;TEXT(F29,"HH:MM:SS")&amp;"'"</f>
+        <v>UNION ALL SELECT 'Everton','Southampton','09 Jul 20 18:00:00'</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="C30" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D30" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E30" s="2">
-        <v>44020</v>
+        <v>44021</v>
       </c>
       <c r="F30" s="1">
-        <v>0.83333333333333337</v>
+        <v>0.84375</v>
       </c>
       <c r="H30" t="str">
-        <f t="shared" si="0"/>
-        <v>UNION ALL SELECT 'West Ham','Burnley','08 Jul 20 20:00:00'</v>
-      </c>
+        <f>"UNION ALL SELECT '"&amp;C30&amp;"','"&amp;D30&amp;"','"&amp;TEXT(E30,"DD MMM YY")&amp;" "&amp;TEXT(F30,"HH:MM:SS")&amp;"'"</f>
+        <v>UNION ALL SELECT 'Aston Villa','Manchester United','09 Jul 20 20:15:00'</v>
+      </c>
+    </row>
+    <row r="33" spans="5:6">
+      <c r="E33" s="2"/>
+      <c r="F33" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
